--- a/read/devices_ip.xlsx
+++ b/read/devices_ip.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12280"/>
+    <workbookView windowWidth="29400" windowHeight="12440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,13 +38,13 @@
     <t>cmds</t>
   </si>
   <si>
-    <t>127.0.0.1</t>
+    <t>192.168.101.10</t>
   </si>
   <si>
     <t>test</t>
   </si>
   <si>
-    <t>dis ver,dis clock</t>
+    <t>dir,display startup,display current-configuration,display interface brief,display dfs-group 1 m-lag,display version,display vlan,display patch-information,display alarm active,display device,display configuration recover-result,display license esn,display license,display system resource mode,display startup feature-software,display interface description,display ip interface brief,display device elabel brief,display bgp peer,display bgp vpnv4 all peer,display lldp neighbor brief</t>
   </si>
 </sst>
 </file>
@@ -937,13 +937,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1198,6 +1191,10 @@
   <sheetPr/>
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="14.5384615384615" customWidth="1"/>
+    <col min="3" max="3" width="25.7692307692308" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
